--- a/database/base_of_recipes.xlsx
+++ b/database/base_of_recipes.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,6 +468,26 @@
       </c>
       <c r="D2" t="n">
         <v>201.01</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-06-02 12:20:30</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>ID: Ervin Senkievich</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>935.3099999999999</v>
       </c>
     </row>
   </sheetData>
